--- a/tests/SAMPLE_Lenovo_Inventory_RICH.xlsx
+++ b/tests/SAMPLE_Lenovo_Inventory_RICH.xlsx
@@ -928,7 +928,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -5285,7 +5285,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -5433,7 +5433,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -6025,7 +6025,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -6264,7 +6264,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -6560,7 +6560,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -7004,7 +7004,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -7061,7 +7061,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -7853,7 +7853,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -8018,7 +8018,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -8566,7 +8566,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -8640,7 +8640,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -8714,7 +8714,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -8788,7 +8788,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -8862,7 +8862,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -8936,7 +8936,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -9306,7 +9306,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -9363,7 +9363,7 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -9780,7 +9780,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -9854,7 +9854,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -9911,7 +9911,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -10372,7 +10372,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -10942,7 +10942,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -11290,7 +11290,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -11347,7 +11347,7 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -11421,7 +11421,7 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
@@ -11438,7 +11438,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -11660,7 +11660,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -11717,7 +11717,7 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
@@ -12452,7 +12452,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
@@ -12800,7 +12800,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -12857,7 +12857,7 @@
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
@@ -13296,7 +13296,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -13518,7 +13518,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -13592,7 +13592,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -13740,7 +13740,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -13814,7 +13814,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -13871,7 +13871,7 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
@@ -14680,7 +14680,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -14976,7 +14976,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -15124,7 +15124,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -15324,7 +15324,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -15768,7 +15768,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -15825,7 +15825,7 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P209" t="inlineStr">
@@ -15842,7 +15842,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -15899,7 +15899,7 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -17256,7 +17256,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -17313,7 +17313,7 @@
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
@@ -18248,7 +18248,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -18396,7 +18396,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -18988,7 +18988,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -19654,7 +19654,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -19711,7 +19711,7 @@
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P263" t="inlineStr">
@@ -19728,7 +19728,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -19785,7 +19785,7 @@
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P264" t="inlineStr">
@@ -19802,7 +19802,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -19859,7 +19859,7 @@
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P265" t="inlineStr">
@@ -19876,7 +19876,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -19933,7 +19933,7 @@
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P266" t="inlineStr">
@@ -20246,7 +20246,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -20986,7 +20986,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -21682,7 +21682,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -21739,7 +21739,7 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P291" t="inlineStr">
@@ -21830,7 +21830,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -21887,7 +21887,7 @@
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P293" t="inlineStr">
@@ -21904,7 +21904,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -22030,7 +22030,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -22326,7 +22326,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -22383,7 +22383,7 @@
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P300" t="inlineStr">
@@ -22622,7 +22622,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -22770,7 +22770,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -22992,7 +22992,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -23049,7 +23049,7 @@
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P309" t="inlineStr">
@@ -23066,7 +23066,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -23362,7 +23362,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -24006,7 +24006,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -24154,7 +24154,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -24302,7 +24302,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -24376,7 +24376,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -24433,7 +24433,7 @@
       </c>
       <c r="O328" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P328" t="inlineStr">
@@ -25464,7 +25464,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -26034,7 +26034,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -26091,7 +26091,7 @@
       </c>
       <c r="O351" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P351" t="inlineStr">
@@ -26182,7 +26182,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -26804,7 +26804,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -26861,7 +26861,7 @@
       </c>
       <c r="O362" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P362" t="inlineStr">
@@ -27248,7 +27248,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -27305,7 +27305,7 @@
       </c>
       <c r="O368" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P368" t="inlineStr">
@@ -27544,7 +27544,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -27601,7 +27601,7 @@
       </c>
       <c r="O372" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P372" t="inlineStr">
@@ -27914,7 +27914,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -28632,7 +28632,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -28689,7 +28689,7 @@
       </c>
       <c r="O387" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P387" t="inlineStr">
@@ -28706,7 +28706,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -29298,7 +29298,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -29355,7 +29355,7 @@
       </c>
       <c r="O396" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P396" t="inlineStr">
@@ -29498,7 +29498,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -29646,7 +29646,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -29920,7 +29920,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -29977,7 +29977,7 @@
       </c>
       <c r="O405" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P405" t="inlineStr">
@@ -29994,7 +29994,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -30051,7 +30051,7 @@
       </c>
       <c r="O406" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P406" t="inlineStr">
@@ -30342,7 +30342,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -30564,7 +30564,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -30838,7 +30838,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -30895,7 +30895,7 @@
       </c>
       <c r="O418" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P418" t="inlineStr">
@@ -30986,7 +30986,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -31043,7 +31043,7 @@
       </c>
       <c r="O420" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P420" t="inlineStr">
@@ -31134,7 +31134,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -31282,7 +31282,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -31430,7 +31430,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -32304,7 +32304,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -32361,7 +32361,7 @@
       </c>
       <c r="O439" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P439" t="inlineStr">
@@ -32452,7 +32452,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -32578,7 +32578,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -33466,7 +33466,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -33762,7 +33762,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -33819,7 +33819,7 @@
       </c>
       <c r="O459" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P459" t="inlineStr">
@@ -33984,7 +33984,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -34206,7 +34206,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -34280,7 +34280,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -34428,7 +34428,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -35242,7 +35242,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -35664,7 +35664,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -35721,7 +35721,7 @@
       </c>
       <c r="O485" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P485" t="inlineStr">
@@ -36108,7 +36108,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -36308,7 +36308,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -36382,7 +36382,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -36826,7 +36826,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -36883,7 +36883,7 @@
       </c>
       <c r="O501" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P501" t="inlineStr">
@@ -37966,7 +37966,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -38114,7 +38114,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -38171,7 +38171,7 @@
       </c>
       <c r="O519" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P519" t="inlineStr">
@@ -38410,7 +38410,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -38467,7 +38467,7 @@
       </c>
       <c r="O523" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P523" t="inlineStr">
@@ -38832,7 +38832,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -39054,7 +39054,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -39128,7 +39128,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -39602,7 +39602,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -39659,7 +39659,7 @@
       </c>
       <c r="O540" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P540" t="inlineStr">
@@ -39676,7 +39676,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
@@ -39824,7 +39824,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -40342,7 +40342,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
@@ -40712,7 +40712,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -41156,7 +41156,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
@@ -41748,7 +41748,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
@@ -41896,7 +41896,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
@@ -41953,7 +41953,7 @@
       </c>
       <c r="O571" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P571" t="inlineStr">
@@ -42044,7 +42044,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -42244,7 +42244,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
@@ -42392,7 +42392,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
@@ -43280,7 +43280,7 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
@@ -43428,7 +43428,7 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
@@ -43576,7 +43576,7 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
@@ -43633,7 +43633,7 @@
       </c>
       <c r="O594" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P594" t="inlineStr">
@@ -43724,7 +43724,7 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
@@ -44412,7 +44412,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -44518,7 +44518,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -44742,7 +44742,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -44798,7 +44798,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -44854,7 +44854,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -44898,7 +44898,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
     </row>
@@ -45293,7 +45293,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -45337,7 +45337,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
     </row>
@@ -45458,7 +45458,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -45617,7 +45617,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -45661,7 +45661,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
     </row>
@@ -45673,7 +45673,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -46009,7 +46009,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -46053,7 +46053,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
     </row>
@@ -46233,7 +46233,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -46560,7 +46560,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -46672,7 +46672,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -46728,7 +46728,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -46837,7 +46837,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -46881,7 +46881,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
     </row>
@@ -47167,7 +47167,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -47556,7 +47556,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -47600,7 +47600,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
     </row>
@@ -47612,7 +47612,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -47656,7 +47656,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
     </row>
@@ -47668,7 +47668,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -47712,7 +47712,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
     </row>
@@ -47724,7 +47724,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -47768,7 +47768,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
     </row>
@@ -48484,7 +48484,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -49133,7 +49133,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -49623,7 +49623,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -49930,7 +49930,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -51444,7 +51444,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -51475,7 +51475,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
     </row>
@@ -51712,7 +51712,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -51738,7 +51738,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
     </row>
@@ -51793,7 +51793,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -51884,7 +51884,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -51920,7 +51920,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
     </row>
@@ -51932,7 +51932,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -52368,7 +52368,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -52480,7 +52480,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">

--- a/tests/SAMPLE_Lenovo_Inventory_RICH.xlsx
+++ b/tests/SAMPLE_Lenovo_Inventory_RICH.xlsx
@@ -928,7 +928,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -5285,7 +5285,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -5433,7 +5433,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -6025,7 +6025,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -6264,7 +6264,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -6560,7 +6560,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -7004,7 +7004,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -7061,7 +7061,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -7853,7 +7853,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -8018,7 +8018,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -8566,7 +8566,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -8640,7 +8640,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -8714,7 +8714,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -8788,7 +8788,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -8862,7 +8862,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -8936,7 +8936,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -9306,7 +9306,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -9363,7 +9363,7 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -9780,7 +9780,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -9854,7 +9854,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -9911,7 +9911,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -10372,7 +10372,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -10942,7 +10942,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -11290,7 +11290,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -11347,7 +11347,7 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -11421,7 +11421,7 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
@@ -11438,7 +11438,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -11660,7 +11660,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -11717,7 +11717,7 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
@@ -12452,7 +12452,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
@@ -12800,7 +12800,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -12857,7 +12857,7 @@
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
@@ -13296,7 +13296,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -13518,7 +13518,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -13592,7 +13592,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -13740,7 +13740,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -13814,7 +13814,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -13871,7 +13871,7 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
@@ -14680,7 +14680,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -14976,7 +14976,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -15124,7 +15124,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -15324,7 +15324,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -15768,7 +15768,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -15825,7 +15825,7 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P209" t="inlineStr">
@@ -15842,7 +15842,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -15899,7 +15899,7 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -17256,7 +17256,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -17313,7 +17313,7 @@
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
@@ -18248,7 +18248,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -18396,7 +18396,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -18988,7 +18988,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -19654,7 +19654,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -19711,7 +19711,7 @@
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P263" t="inlineStr">
@@ -19728,7 +19728,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -19785,7 +19785,7 @@
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P264" t="inlineStr">
@@ -19802,7 +19802,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -19859,7 +19859,7 @@
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P265" t="inlineStr">
@@ -19876,7 +19876,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -19933,7 +19933,7 @@
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P266" t="inlineStr">
@@ -20246,7 +20246,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -20986,7 +20986,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -21682,7 +21682,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -21739,7 +21739,7 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P291" t="inlineStr">
@@ -21830,7 +21830,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -21887,7 +21887,7 @@
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P293" t="inlineStr">
@@ -21904,7 +21904,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -22030,7 +22030,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -22326,7 +22326,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -22383,7 +22383,7 @@
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P300" t="inlineStr">
@@ -22622,7 +22622,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -22770,7 +22770,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -22992,7 +22992,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -23049,7 +23049,7 @@
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P309" t="inlineStr">
@@ -23066,7 +23066,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -23362,7 +23362,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -24006,7 +24006,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -24154,7 +24154,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -24302,7 +24302,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -24376,7 +24376,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -24433,7 +24433,7 @@
       </c>
       <c r="O328" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P328" t="inlineStr">
@@ -25464,7 +25464,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -26034,7 +26034,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -26091,7 +26091,7 @@
       </c>
       <c r="O351" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P351" t="inlineStr">
@@ -26182,7 +26182,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -26804,7 +26804,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -26861,7 +26861,7 @@
       </c>
       <c r="O362" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P362" t="inlineStr">
@@ -27248,7 +27248,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -27305,7 +27305,7 @@
       </c>
       <c r="O368" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P368" t="inlineStr">
@@ -27544,7 +27544,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -27601,7 +27601,7 @@
       </c>
       <c r="O372" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P372" t="inlineStr">
@@ -27914,7 +27914,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -28632,7 +28632,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -28689,7 +28689,7 @@
       </c>
       <c r="O387" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P387" t="inlineStr">
@@ -28706,7 +28706,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -29298,7 +29298,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -29355,7 +29355,7 @@
       </c>
       <c r="O396" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P396" t="inlineStr">
@@ -29498,7 +29498,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -29646,7 +29646,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -29920,7 +29920,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -29977,7 +29977,7 @@
       </c>
       <c r="O405" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P405" t="inlineStr">
@@ -29994,7 +29994,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -30051,7 +30051,7 @@
       </c>
       <c r="O406" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P406" t="inlineStr">
@@ -30342,7 +30342,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -30564,7 +30564,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -30838,7 +30838,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -30895,7 +30895,7 @@
       </c>
       <c r="O418" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P418" t="inlineStr">
@@ -30986,7 +30986,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -31043,7 +31043,7 @@
       </c>
       <c r="O420" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P420" t="inlineStr">
@@ -31134,7 +31134,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -31282,7 +31282,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -31430,7 +31430,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -32304,7 +32304,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -32361,7 +32361,7 @@
       </c>
       <c r="O439" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P439" t="inlineStr">
@@ -32452,7 +32452,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -32578,7 +32578,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -33466,7 +33466,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -33762,7 +33762,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -33819,7 +33819,7 @@
       </c>
       <c r="O459" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P459" t="inlineStr">
@@ -33984,7 +33984,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -34206,7 +34206,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -34280,7 +34280,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -34428,7 +34428,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -35242,7 +35242,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -35664,7 +35664,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -35721,7 +35721,7 @@
       </c>
       <c r="O485" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P485" t="inlineStr">
@@ -36108,7 +36108,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -36308,7 +36308,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -36382,7 +36382,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -36826,7 +36826,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -36883,7 +36883,7 @@
       </c>
       <c r="O501" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P501" t="inlineStr">
@@ -37966,7 +37966,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -38114,7 +38114,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -38171,7 +38171,7 @@
       </c>
       <c r="O519" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P519" t="inlineStr">
@@ -38410,7 +38410,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -38467,7 +38467,7 @@
       </c>
       <c r="O523" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P523" t="inlineStr">
@@ -38832,7 +38832,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -39054,7 +39054,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -39128,7 +39128,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -39602,7 +39602,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -39659,7 +39659,7 @@
       </c>
       <c r="O540" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P540" t="inlineStr">
@@ -39676,7 +39676,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
@@ -39824,7 +39824,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -40342,7 +40342,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
@@ -40712,7 +40712,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -41156,7 +41156,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
@@ -41748,7 +41748,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
@@ -41896,7 +41896,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
@@ -41953,7 +41953,7 @@
       </c>
       <c r="O571" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P571" t="inlineStr">
@@ -42044,7 +42044,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -42244,7 +42244,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
@@ -42392,7 +42392,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
@@ -43280,7 +43280,7 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
@@ -43428,7 +43428,7 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
@@ -43576,7 +43576,7 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
@@ -43633,7 +43633,7 @@
       </c>
       <c r="O594" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P594" t="inlineStr">
@@ -43724,7 +43724,7 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
@@ -44412,7 +44412,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -44518,7 +44518,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -44742,7 +44742,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -44798,7 +44798,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -44854,7 +44854,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -44898,7 +44898,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
     </row>
@@ -45293,7 +45293,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -45337,7 +45337,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
     </row>
@@ -45458,7 +45458,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -45617,7 +45617,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -45661,7 +45661,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
     </row>
@@ -45673,7 +45673,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -46009,7 +46009,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -46053,7 +46053,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
     </row>
@@ -46233,7 +46233,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -46560,7 +46560,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -46672,7 +46672,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -46728,7 +46728,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -46837,7 +46837,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -46881,7 +46881,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
     </row>
@@ -47167,7 +47167,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -47556,7 +47556,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -47600,7 +47600,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
     </row>
@@ -47612,7 +47612,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -47656,7 +47656,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
     </row>
@@ -47668,7 +47668,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -47712,7 +47712,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
     </row>
@@ -47724,7 +47724,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -47768,7 +47768,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
     </row>
@@ -48484,7 +48484,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -49133,7 +49133,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -49623,7 +49623,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -49930,7 +49930,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -51444,7 +51444,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -51475,7 +51475,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
     </row>
@@ -51712,7 +51712,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -51738,7 +51738,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
     </row>
@@ -51793,7 +51793,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -51884,7 +51884,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -51920,7 +51920,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
     </row>
@@ -51932,7 +51932,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -52368,7 +52368,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -52480,7 +52480,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
